--- a/sensibilidad_supuestos.xlsx
+++ b/sensibilidad_supuestos.xlsx
@@ -471,13 +471,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.513</v>
+        <v>0.502</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.029</v>
+        <v>0.016</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="E3" t="n">
         <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.101</v>
+        <v>0.108</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.003</v>
+        <v>1.063</v>
       </c>
       <c r="E4" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="F4" t="n">
-        <v>0.316</v>
+        <v>0.372</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
@@ -564,10 +564,10 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.384</v>
+        <v>0.479</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="E6" t="n">
         <v>0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>0.101</v>
+        <v>0.108</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.552</v>
+        <v>0.54</v>
       </c>
       <c r="E7" t="n">
         <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.543</v>
+        <v>0.533</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F8" t="n">
-        <v>0.101</v>
+        <v>0.108</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="E9" t="n">
         <v>0.08</v>
       </c>
       <c r="F9" t="n">
-        <v>0.101</v>
+        <v>0.108</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.594</v>
+        <v>0.595</v>
       </c>
       <c r="E10" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="F10" t="n">
-        <v>0.101</v>
+        <v>0.107</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -732,13 +732,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.646</v>
+        <v>0.634</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>0.026</v>
+        <v>0.016</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.674</v>
+        <v>0.664</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>0.096</v>
+        <v>0.106</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.832</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="F13" t="n">
-        <v>0.279</v>
+        <v>0.372</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.703</v>
+        <v>0.711</v>
       </c>
       <c r="E14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.327</v>
+        <v>0.473</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.674</v>
+        <v>0.664</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>0.096</v>
+        <v>0.106</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.668</v>
+        <v>0.654</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F16" t="n">
-        <v>0.052</v>
+        <v>0.028</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.672</v>
+        <v>0.651</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="F17" t="n">
-        <v>0.096</v>
+        <v>0.106</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.674</v>
+        <v>0.664</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F18" t="n">
-        <v>0.096</v>
+        <v>0.106</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.702</v>
+        <v>0.7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="F19" t="n">
-        <v>0.096</v>
+        <v>0.105</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.534</v>
+        <v>0.537</v>
       </c>
       <c r="E20" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="F20" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -1022,16 +1022,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.703</v>
+        <v>0.737</v>
       </c>
       <c r="E21" t="n">
-        <v>0.88</v>
+        <v>1.15</v>
       </c>
       <c r="F21" t="n">
         <v>0.112</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.266</v>
+        <v>1.325</v>
       </c>
       <c r="E22" t="n">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
       <c r="F22" t="n">
-        <v>0.295</v>
+        <v>0.362</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23">
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.744</v>
+        <v>0.781</v>
       </c>
       <c r="E23" t="n">
-        <v>0.88</v>
+        <v>1.14</v>
       </c>
       <c r="F23" t="n">
-        <v>0.429</v>
+        <v>0.464</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.703</v>
+        <v>0.737</v>
       </c>
       <c r="E24" t="n">
-        <v>0.88</v>
+        <v>1.15</v>
       </c>
       <c r="F24" t="n">
         <v>0.112</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.727</v>
       </c>
       <c r="E25" t="n">
-        <v>0.88</v>
+        <v>1.16</v>
       </c>
       <c r="F25" t="n">
-        <v>0.035</v>
+        <v>0.028</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.632</v>
+        <v>0.654</v>
       </c>
       <c r="E26" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="F26" t="n">
         <v>0.112</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.703</v>
+        <v>0.737</v>
       </c>
       <c r="E27" t="n">
-        <v>0.88</v>
+        <v>1.15</v>
       </c>
       <c r="F27" t="n">
         <v>0.112</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
@@ -1225,16 +1225,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.825</v>
+        <v>0.864</v>
       </c>
       <c r="E28" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="F28" t="n">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.495</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="3">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="4">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.092</v>
+        <v>1.156</v>
       </c>
     </row>
   </sheetData>
